--- a/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/tables/wilks_importance.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/tables/wilks_importance.xlsx
@@ -477,27 +477,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1970843670597916</v>
+        <v>0.1891469992904127</v>
       </c>
       <c r="C2" t="n">
-        <v>6.201930765151319</v>
+        <v>9.350458678290126</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004667409969532299</v>
+        <v>0.0004512928684461404</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>***</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.8835172157760413</v>
+        <v>-0.5767078409113812</v>
       </c>
       <c r="G2" t="n">
-        <v>1.220481676442706</v>
+        <v>2.262324200535749</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1537355033596803</v>
+        <v>-0.3103718420711152</v>
       </c>
     </row>
     <row r="3">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04003201600365724</v>
+        <v>0.06367438415390309</v>
       </c>
       <c r="C3" t="n">
-        <v>1.259743709498733</v>
+        <v>3.147735359959372</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2953067830399284</v>
+        <v>0.05348946346510941</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,29 +521,29 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-0.4751060955337392</v>
+        <v>-0.07858299295170462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2510438523012383</v>
+        <v>-0.6379884882146052</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2272365501817642</v>
+        <v>1.022246146929286</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01945036819900237</v>
+        <v>0.03917451005205752</v>
       </c>
       <c r="C4" t="n">
-        <v>0.612072072110706</v>
+        <v>1.936587092886499</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5474850789222676</v>
+        <v>0.1571592119733994</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-0.09480683543729562</v>
+        <v>0.2229947105611539</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1982903217739131</v>
+        <v>-1.013225217956377</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2352868655659003</v>
+        <v>0.2757738667764528</v>
       </c>
     </row>
     <row r="5">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01903582871959786</v>
+        <v>0.02690853560508943</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5990271757090109</v>
+        <v>1.330220152646326</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5544503108314758</v>
+        <v>0.2755895744016933</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -581,29 +581,29 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.2784817410740543</v>
+        <v>-0.2229743364018089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3241955834046125</v>
+        <v>0.6955269096210195</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00219508636171456</v>
+        <v>0.0815577802333626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01609197604566115</v>
+        <v>0.01275854464727294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5063888262603098</v>
+        <v>0.6307170875932165</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6066773169445743</v>
+        <v>0.537294413892246</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1781704063359165</v>
+        <v>0.05633632395645205</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3380713845302415</v>
+        <v>0.1812596862028683</v>
       </c>
       <c r="H6" t="n">
-        <v>0.101315994344376</v>
+        <v>-0.4222204023094785</v>
       </c>
     </row>
   </sheetData>
